--- a/data/trans_dic/P12_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P12_1_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se sintió calmada y tranquila alguna vez o algunas veces</t>
+          <t>Población que se sintió calmada y tranquila alguna vez o algunas veces (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,68; 17,19</t>
+          <t>8,79; 16,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,58; 28,78</t>
+          <t>19,04; 28,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,95; 29,53</t>
+          <t>19,6; 29,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,32</t>
+          <t>2,14; 6,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,71; 23,1</t>
+          <t>12,82; 22,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,16; 47,96</t>
+          <t>35,28; 47,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,1; 38,18</t>
+          <t>27,73; 38,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,72</t>
+          <t>3,78; 7,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,26; 18,7</t>
+          <t>12,08; 18,4</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,45; 36,65</t>
+          <t>28,5; 36,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,66; 32,63</t>
+          <t>24,85; 32,56</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,21</t>
+          <t>3,38; 6,32</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,29; 26,55</t>
+          <t>18,4; 26,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,58; 14,17</t>
+          <t>8,54; 14,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,79</t>
+          <t>3,84; 7,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,92; 16,29</t>
+          <t>9,26; 16,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,71; 39,39</t>
+          <t>30,99; 39,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,79; 23,79</t>
+          <t>16,74; 23,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 12,39</t>
+          <t>6,85; 11,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,68; 19,29</t>
+          <t>13,62; 19,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,01; 31,77</t>
+          <t>25,84; 31,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,51; 17,97</t>
+          <t>13,73; 18,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 8,95</t>
+          <t>5,67; 9,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,93; 16,78</t>
+          <t>12,06; 17,0</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 9,07</t>
+          <t>3,46; 9,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,64; 18,29</t>
+          <t>10,69; 18,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,79; 15,49</t>
+          <t>8,98; 16,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,22; 12,03</t>
+          <t>6,14; 12,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,82; 12,06</t>
+          <t>6,06; 12,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,93; 27,55</t>
+          <t>18,29; 27,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,69; 19,51</t>
+          <t>11,59; 19,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,23; 16,93</t>
+          <t>11,48; 17,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 9,92</t>
+          <t>5,68; 9,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,51; 21,59</t>
+          <t>15,51; 21,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,18; 16,27</t>
+          <t>11,4; 16,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,71; 13,88</t>
+          <t>9,69; 13,82</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,0; 17,62</t>
+          <t>10,01; 17,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,22; 22,32</t>
+          <t>13,82; 22,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,0; 21,54</t>
+          <t>13,91; 21,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,8; 20,39</t>
+          <t>10,89; 20,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,65; 22,89</t>
+          <t>14,66; 22,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,88; 40,45</t>
+          <t>31,77; 41,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,82; 31,3</t>
+          <t>22,44; 31,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,88; 18,12</t>
+          <t>8,64; 18,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,41; 18,61</t>
+          <t>13,4; 18,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,65; 30,29</t>
+          <t>23,63; 30,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19,0; 25,41</t>
+          <t>19,12; 25,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,57; 17,62</t>
+          <t>10,52; 17,53</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,06; 30,76</t>
+          <t>18,95; 30,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,05; 15,65</t>
+          <t>6,87; 15,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,47; 25,34</t>
+          <t>14,66; 25,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32,79; 44,79</t>
+          <t>32,49; 45,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,99; 38,62</t>
+          <t>26,62; 39,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,49; 32,35</t>
+          <t>20,98; 33,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,25; 28,71</t>
+          <t>16,78; 28,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>44,08; 53,44</t>
+          <t>43,7; 53,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24,21; 32,64</t>
+          <t>24,42; 32,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,98; 22,79</t>
+          <t>14,97; 22,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,22; 24,83</t>
+          <t>17,53; 24,75</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>40,12; 47,7</t>
+          <t>40,1; 47,88</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,54; 13,84</t>
+          <t>6,78; 13,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,63; 18,63</t>
+          <t>9,71; 19,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,43; 14,89</t>
+          <t>7,57; 15,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,73; 17,23</t>
+          <t>9,88; 17,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,31; 19,39</t>
+          <t>10,88; 19,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,59; 28,71</t>
+          <t>18,22; 28,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,13; 24,21</t>
+          <t>14,84; 24,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,91; 19,48</t>
+          <t>12,42; 19,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,66; 15,13</t>
+          <t>9,58; 14,96</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15,33; 22,14</t>
+          <t>15,61; 22,16</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,03; 18,21</t>
+          <t>11,94; 18,06</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,07; 16,84</t>
+          <t>11,88; 16,76</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,28; 14,61</t>
+          <t>9,14; 14,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,16; 19,95</t>
+          <t>14,24; 20,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,69; 16,21</t>
+          <t>10,79; 16,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,68; 21,38</t>
+          <t>14,74; 21,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,1; 20,55</t>
+          <t>14,44; 20,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,1; 26,64</t>
+          <t>19,97; 26,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,12; 20,21</t>
+          <t>14,23; 20,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26,1; 69,62</t>
+          <t>26,3; 72,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,45; 16,57</t>
+          <t>12,65; 16,34</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,2; 22,48</t>
+          <t>17,87; 22,56</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13,26; 17,35</t>
+          <t>13,25; 17,41</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,93; 60,84</t>
+          <t>21,79; 57,13</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>23,33; 29,75</t>
+          <t>22,86; 29,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,08; 19,85</t>
+          <t>13,84; 19,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,55; 6,46</t>
+          <t>3,69; 6,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,16; 10,84</t>
+          <t>3,43; 11,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,51; 30,89</t>
+          <t>24,88; 31,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,88; 26,96</t>
+          <t>20,91; 26,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,82; 11,14</t>
+          <t>6,83; 11,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,87; 19,41</t>
+          <t>15,07; 19,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24,82; 29,37</t>
+          <t>24,94; 29,59</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18,26; 22,5</t>
+          <t>18,13; 22,66</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,68; 8,33</t>
+          <t>5,75; 8,42</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,21; 14,11</t>
+          <t>7,25; 14,19</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,61; 18,21</t>
+          <t>15,67; 18,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14,48; 17,05</t>
+          <t>14,58; 17,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,46; 12,77</t>
+          <t>10,56; 12,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,69; 14,06</t>
+          <t>9,87; 14,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,9; 23,79</t>
+          <t>21,05; 23,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,45; 27,51</t>
+          <t>24,55; 27,52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,38; 18,03</t>
+          <t>15,43; 18,01</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18,59; 38,01</t>
+          <t>18,47; 38,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18,66; 20,82</t>
+          <t>18,77; 20,68</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19,97; 22,05</t>
+          <t>20,01; 22,04</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13,37; 15,12</t>
+          <t>13,41; 15,11</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,19; 26,29</t>
+          <t>15,23; 26,56</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se sintió calmada y tranquila alguna vez o algunas veces</t>
+          <t>Población que se sintió calmada y tranquila alguna vez o algunas veces (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23694; 46926</t>
+          <t>23988; 46090</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>54759; 84816</t>
+          <t>56110; 84160</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55674; 86757</t>
+          <t>57587; 86032</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5969; 19680</t>
+          <t>6674; 21102</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>35752; 60251</t>
+          <t>33446; 59127</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>100637; 137257</t>
+          <t>100963; 136850</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>78242; 110235</t>
+          <t>80050; 111514</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11091; 22357</t>
+          <t>10940; 21962</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65438; 99839</t>
+          <t>64485; 98216</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>165276; 212894</t>
+          <t>165556; 210627</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>143656; 190058</t>
+          <t>144731; 189657</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20418; 37345</t>
+          <t>20294; 38009</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90169; 130922</t>
+          <t>90742; 131006</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43360; 71650</t>
+          <t>43168; 74293</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18407; 39064</t>
+          <t>19231; 38373</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46252; 84457</t>
+          <t>47997; 85026</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>154738; 198500</t>
+          <t>156174; 196813</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87266; 123640</t>
+          <t>87004; 124245</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35743; 64651</t>
+          <t>35757; 61389</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>70424; 99321</t>
+          <t>70114; 99717</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>259345; 316749</t>
+          <t>257619; 315000</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>138515; 184267</t>
+          <t>140763; 190247</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58586; 91628</t>
+          <t>58059; 92759</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>123278; 173392</t>
+          <t>124660; 175681</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12025; 28907</t>
+          <t>11018; 30088</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34481; 59261</t>
+          <t>34652; 60812</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27991; 49342</t>
+          <t>28611; 50990</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19654; 38011</t>
+          <t>19395; 38852</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>19518; 40440</t>
+          <t>20321; 42015</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61159; 93964</t>
+          <t>62384; 95138</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39086; 65236</t>
+          <t>38746; 64679</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39126; 59005</t>
+          <t>40023; 61215</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37257; 64906</t>
+          <t>37159; 63349</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>103126; 143602</t>
+          <t>103154; 143403</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>73028; 106246</t>
+          <t>74421; 108171</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>64532; 92260</t>
+          <t>64417; 91830</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35872; 63182</t>
+          <t>35896; 61290</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52879; 83035</t>
+          <t>51397; 82413</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51793; 79686</t>
+          <t>51456; 79537</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33671; 63553</t>
+          <t>33964; 63544</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54421; 85030</t>
+          <t>54444; 83328</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>120102; 157334</t>
+          <t>123558; 160401</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>84127; 120649</t>
+          <t>86499; 122704</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37487; 86176</t>
+          <t>41117; 86896</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>97891; 135869</t>
+          <t>97820; 135906</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>179985; 230471</t>
+          <t>179846; 229695</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>143558; 191959</t>
+          <t>144478; 190349</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>83229; 138715</t>
+          <t>82821; 138046</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>38756; 62539</t>
+          <t>38530; 62311</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14986; 33277</t>
+          <t>14602; 33499</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30568; 53513</t>
+          <t>30969; 53776</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58610; 80050</t>
+          <t>58064; 80555</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>53982; 80202</t>
+          <t>55277; 82122</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44994; 71037</t>
+          <t>46061; 72992</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37708; 62752</t>
+          <t>36677; 62282</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>91787; 111271</t>
+          <t>90997; 111728</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>99480; 134147</t>
+          <t>100341; 134314</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>64750; 98521</t>
+          <t>64699; 97776</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74002; 106706</t>
+          <t>75352; 106373</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>155235; 184592</t>
+          <t>155175; 185294</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17709; 37483</t>
+          <t>18356; 36605</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26395; 51056</t>
+          <t>26611; 52460</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19548; 39172</t>
+          <t>19926; 40104</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26231; 46468</t>
+          <t>26640; 46078</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>28686; 53941</t>
+          <t>30264; 53347</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>51880; 80130</t>
+          <t>50857; 78853</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38599; 66120</t>
+          <t>40522; 67869</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>33180; 50084</t>
+          <t>31926; 49280</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53007; 83061</t>
+          <t>52605; 82137</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>84796; 122458</t>
+          <t>86319; 122586</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64528; 97657</t>
+          <t>64018; 96856</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>63571; 88683</t>
+          <t>62552; 88252</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>57046; 89827</t>
+          <t>56238; 88661</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>93875; 132209</t>
+          <t>94379; 135823</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>70215; 106422</t>
+          <t>70857; 107386</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>91631; 133466</t>
+          <t>92002; 132947</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>90015; 131168</t>
+          <t>92129; 130409</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>139289; 184564</t>
+          <t>138379; 184584</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>97421; 139481</t>
+          <t>98166; 138426</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>221690; 591246</t>
+          <t>223334; 614950</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>156054; 207631</t>
+          <t>158526; 204761</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>246787; 304740</t>
+          <t>242318; 305866</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>178617; 233642</t>
+          <t>178404; 234432</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>323136; 896570</t>
+          <t>321095; 841895</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>173562; 221314</t>
+          <t>169995; 220138</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>109545; 154392</t>
+          <t>107644; 151953</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>27580; 50256</t>
+          <t>28719; 52628</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>29375; 100691</t>
+          <t>31899; 102243</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>192001; 242008</t>
+          <t>194909; 244969</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>171837; 221812</t>
+          <t>172012; 221476</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>56339; 92039</t>
+          <t>56414; 91953</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>106717; 139332</t>
+          <t>108177; 139098</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>379107; 448501</t>
+          <t>380909; 451952</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>292238; 360153</t>
+          <t>290277; 362805</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>91123; 133626</t>
+          <t>92140; 134979</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>118705; 232351</t>
+          <t>119352; 233563</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>511610; 596679</t>
+          <t>513326; 598104</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>495880; 583831</t>
+          <t>499111; 596268</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>354814; 433259</t>
+          <t>358217; 431445</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>335345; 486187</t>
+          <t>341352; 487179</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>706186; 803807</t>
+          <t>711226; 805335</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>867953; 976539</t>
+          <t>871659; 977191</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>544270; 637888</t>
+          <t>545872; 637115</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>680531; 1391476</t>
+          <t>676326; 1420058</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1242138; 1385570</t>
+          <t>1249092; 1376110</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1392870; 1538054</t>
+          <t>1395615; 1537357</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>926931; 1047567</t>
+          <t>929739; 1047161</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1081742; 1871800</t>
+          <t>1084551; 1891444</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P12_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P12_1_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,79; 16,88</t>
+          <t>8,58; 16,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,04; 28,55</t>
+          <t>18,91; 28,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,6; 29,29</t>
+          <t>18,84; 29,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,78</t>
+          <t>1,87; 5,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,82; 22,67</t>
+          <t>13,54; 23,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,28; 47,82</t>
+          <t>35,28; 47,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,73; 38,63</t>
+          <t>27,12; 38,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 7,58</t>
+          <t>3,91; 7,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,08; 18,4</t>
+          <t>11,93; 18,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,5; 36,26</t>
+          <t>28,43; 36,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,85; 32,56</t>
+          <t>24,59; 32,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,32</t>
+          <t>3,36; 6,03</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,4; 26,57</t>
+          <t>18,69; 26,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,54; 14,7</t>
+          <t>8,36; 14,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,65</t>
+          <t>3,63; 7,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,26; 16,4</t>
+          <t>9,21; 16,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,99; 39,05</t>
+          <t>31,05; 39,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,74; 23,9</t>
+          <t>16,85; 24,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 11,76</t>
+          <t>6,75; 11,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,62; 19,36</t>
+          <t>13,62; 19,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,84; 31,59</t>
+          <t>26,04; 31,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,73; 18,55</t>
+          <t>13,29; 18,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,67; 9,06</t>
+          <t>5,82; 9,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,06; 17,0</t>
+          <t>12,39; 16,78</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 9,44</t>
+          <t>3,74; 9,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,69; 18,77</t>
+          <t>10,64; 18,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,98; 16,01</t>
+          <t>8,65; 15,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,14; 12,29</t>
+          <t>6,07; 12,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,06; 12,53</t>
+          <t>5,86; 11,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,29; 27,9</t>
+          <t>17,96; 27,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,59; 19,34</t>
+          <t>11,84; 19,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,48; 17,56</t>
+          <t>11,12; 17,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,68; 9,68</t>
+          <t>5,79; 9,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,51; 21,56</t>
+          <t>15,39; 21,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,4; 16,57</t>
+          <t>11,12; 16,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,69; 13,82</t>
+          <t>9,54; 13,61</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,01; 17,09</t>
+          <t>9,83; 16,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,82; 22,16</t>
+          <t>13,59; 21,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,91; 21,5</t>
+          <t>13,93; 22,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,89; 20,38</t>
+          <t>10,19; 19,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,66; 22,43</t>
+          <t>14,96; 23,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,77; 41,24</t>
+          <t>30,61; 40,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,44; 31,83</t>
+          <t>22,04; 31,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,64; 18,27</t>
+          <t>14,46; 21,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,4; 18,61</t>
+          <t>13,41; 18,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,63; 30,19</t>
+          <t>23,43; 30,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19,12; 25,2</t>
+          <t>19,1; 25,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,52; 17,53</t>
+          <t>13,2; 18,93</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>42,83%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,95; 30,65</t>
+          <t>18,75; 30,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,87; 15,76</t>
+          <t>6,8; 15,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,66; 25,46</t>
+          <t>14,32; 25,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32,49; 45,07</t>
+          <t>31,6; 42,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,62; 39,54</t>
+          <t>25,94; 39,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,98; 33,24</t>
+          <t>20,55; 33,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,78; 28,49</t>
+          <t>17,02; 28,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>43,7; 53,66</t>
+          <t>43,55; 52,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24,42; 32,68</t>
+          <t>24,41; 33,14</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,97; 22,62</t>
+          <t>15,18; 22,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,53; 24,75</t>
+          <t>17,16; 24,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>40,1; 47,88</t>
+          <t>38,97; 47,03</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,78; 13,52</t>
+          <t>6,51; 13,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,71; 19,15</t>
+          <t>9,96; 18,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,57; 15,24</t>
+          <t>7,42; 14,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,88; 17,09</t>
+          <t>9,73; 16,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,88; 19,18</t>
+          <t>10,12; 18,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,22; 28,25</t>
+          <t>18,4; 28,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,84; 24,85</t>
+          <t>14,05; 24,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,42; 19,17</t>
+          <t>12,25; 18,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,58; 14,96</t>
+          <t>9,71; 15,14</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15,61; 22,16</t>
+          <t>15,51; 22,65</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,94; 18,06</t>
+          <t>11,98; 18,28</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,88; 16,76</t>
+          <t>11,68; 16,49</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,14; 14,42</t>
+          <t>9,19; 14,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,24; 20,49</t>
+          <t>14,11; 20,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,79; 16,36</t>
+          <t>10,9; 16,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,74; 21,3</t>
+          <t>14,63; 21,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,44; 20,43</t>
+          <t>14,47; 20,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,97; 26,64</t>
+          <t>20,26; 26,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,23; 20,06</t>
+          <t>14,45; 20,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26,3; 72,41</t>
+          <t>23,61; 29,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,65; 16,34</t>
+          <t>12,58; 16,44</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,87; 22,56</t>
+          <t>18,27; 22,63</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13,25; 17,41</t>
+          <t>13,42; 17,57</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,79; 57,13</t>
+          <t>20,23; 24,57</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>22,86; 29,6</t>
+          <t>23,03; 29,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,84; 19,53</t>
+          <t>13,78; 19,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,69; 6,77</t>
+          <t>3,59; 6,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,43; 11,01</t>
+          <t>7,72; 11,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,88; 31,27</t>
+          <t>24,93; 31,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,91; 26,92</t>
+          <t>20,66; 27,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,83; 11,13</t>
+          <t>6,82; 11,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,07; 19,38</t>
+          <t>15,12; 19,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24,94; 29,59</t>
+          <t>24,76; 29,48</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18,13; 22,66</t>
+          <t>18,21; 22,51</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,75; 8,42</t>
+          <t>5,78; 8,43</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,25; 14,19</t>
+          <t>12,07; 15,07</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,67; 18,25</t>
+          <t>15,64; 18,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14,58; 17,42</t>
+          <t>14,47; 17,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,56; 12,72</t>
+          <t>10,62; 12,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,87; 14,08</t>
+          <t>12,18; 14,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,05; 23,83</t>
+          <t>21,04; 23,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,55; 27,52</t>
+          <t>24,43; 27,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,43; 18,01</t>
+          <t>15,32; 18,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18,47; 38,79</t>
+          <t>18,39; 20,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18,77; 20,68</t>
+          <t>18,66; 20,69</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20,01; 22,04</t>
+          <t>19,94; 21,97</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13,41; 15,11</t>
+          <t>13,36; 15,08</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,23; 26,56</t>
+          <t>15,67; 17,33</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>10954</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16035</t>
+          <t>17340</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27886</t>
+          <t>28294</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23988; 46090</t>
+          <t>23417; 46376</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>56110; 84160</t>
+          <t>55748; 84214</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57587; 86032</t>
+          <t>55358; 85237</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6674; 21102</t>
+          <t>5961; 18036</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>33446; 59127</t>
+          <t>35327; 60057</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>100963; 136850</t>
+          <t>100979; 135353</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80050; 111514</t>
+          <t>78287; 110352</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10940; 21962</t>
+          <t>12346; 23630</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>64485; 98216</t>
+          <t>63700; 98747</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>165556; 210627</t>
+          <t>165148; 211966</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>144731; 189657</t>
+          <t>143202; 190622</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20294; 38009</t>
+          <t>21314; 38288</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63887</t>
+          <t>65828</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>83842</t>
+          <t>89241</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>147729</t>
+          <t>155069</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90742; 131006</t>
+          <t>92149; 130331</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43168; 74293</t>
+          <t>42285; 71504</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19231; 38373</t>
+          <t>18218; 39280</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47997; 85026</t>
+          <t>48862; 85961</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>156174; 196813</t>
+          <t>156495; 199217</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87004; 124245</t>
+          <t>87569; 125057</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35757; 61389</t>
+          <t>35212; 61091</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>70114; 99717</t>
+          <t>74457; 104755</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>257619; 315000</t>
+          <t>259626; 315503</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>140763; 190247</t>
+          <t>136272; 187108</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58059; 92759</t>
+          <t>59526; 92749</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>124660; 175681</t>
+          <t>133464; 180708</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28203</t>
+          <t>27272</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49073</t>
+          <t>49745</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77275</t>
+          <t>77017</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11018; 30088</t>
+          <t>11920; 28767</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34652; 60812</t>
+          <t>34484; 59095</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28611; 50990</t>
+          <t>27543; 49699</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19395; 38852</t>
+          <t>19165; 38202</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20321; 42015</t>
+          <t>19667; 39741</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62384; 95138</t>
+          <t>61241; 93018</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38746; 64679</t>
+          <t>39579; 66225</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>40023; 61215</t>
+          <t>39552; 61467</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37159; 63349</t>
+          <t>37864; 65329</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>103154; 143403</t>
+          <t>102358; 142189</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74421; 108171</t>
+          <t>72631; 107003</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>64417; 91830</t>
+          <t>64083; 91416</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46944</t>
+          <t>52086</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>65753</t>
+          <t>73675</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>112697</t>
+          <t>125761</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35896; 61290</t>
+          <t>35269; 60226</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51397; 82413</t>
+          <t>50552; 81487</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51456; 79537</t>
+          <t>51523; 81642</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33964; 63544</t>
+          <t>37941; 71547</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54444; 83328</t>
+          <t>55559; 85958</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>123558; 160401</t>
+          <t>119046; 157101</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86499; 122704</t>
+          <t>84963; 122774</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>41117; 86896</t>
+          <t>61002; 88924</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>97820; 135906</t>
+          <t>97875; 138069</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>179846; 229695</t>
+          <t>178291; 229819</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>144478; 190349</t>
+          <t>144322; 192105</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>82821; 138046</t>
+          <t>104852; 150316</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68548</t>
+          <t>76658</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>101273</t>
+          <t>108548</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>169821</t>
+          <t>185206</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>38530; 62311</t>
+          <t>38119; 61822</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14602; 33499</t>
+          <t>14452; 33815</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30969; 53776</t>
+          <t>30244; 53573</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58064; 80555</t>
+          <t>64986; 88065</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>55277; 82122</t>
+          <t>53866; 81085</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46061; 72992</t>
+          <t>45121; 72801</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36677; 62282</t>
+          <t>37209; 63091</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>90997; 111728</t>
+          <t>98759; 120134</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>100341; 134314</t>
+          <t>100329; 136202</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>64699; 97776</t>
+          <t>65627; 98213</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>75352; 106373</t>
+          <t>73759; 106698</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>155175; 185294</t>
+          <t>168525; 203365</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35597</t>
+          <t>34333</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>39997</t>
+          <t>40284</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>75594</t>
+          <t>74617</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18356; 36605</t>
+          <t>17641; 37760</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26611; 52460</t>
+          <t>27283; 51028</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19926; 40104</t>
+          <t>19517; 38906</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26640; 46078</t>
+          <t>26330; 44331</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30264; 53347</t>
+          <t>28162; 52090</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>50857; 78853</t>
+          <t>51344; 78472</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40522; 67869</t>
+          <t>38370; 66359</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>31926; 49280</t>
+          <t>32304; 49676</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52605; 82137</t>
+          <t>53297; 83111</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>86319; 122586</t>
+          <t>85772; 125254</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64018; 96856</t>
+          <t>64223; 98037</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>62552; 88252</t>
+          <t>62398; 88126</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>111066</t>
+          <t>127372</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>380660</t>
+          <t>205880</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>491727</t>
+          <t>333252</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>56238; 88661</t>
+          <t>56532; 90083</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>94379; 135823</t>
+          <t>93549; 134677</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>70857; 107386</t>
+          <t>71542; 108603</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>92002; 132947</t>
+          <t>105296; 151109</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>92129; 130409</t>
+          <t>92370; 129923</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>138379; 184584</t>
+          <t>140353; 186090</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98166; 138426</t>
+          <t>99741; 138873</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>223334; 614950</t>
+          <t>182313; 229349</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>158526; 204761</t>
+          <t>157665; 206087</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>242318; 305866</t>
+          <t>247714; 306829</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>178404; 234432</t>
+          <t>180680; 236532</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>321095; 841895</t>
+          <t>301774; 366578</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>68899</t>
+          <t>77591</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>121871</t>
+          <t>142879</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>190770</t>
+          <t>220470</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>169995; 220138</t>
+          <t>171270; 222448</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>107644; 151953</t>
+          <t>107215; 151588</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>28719; 52628</t>
+          <t>27953; 52159</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>31899; 102243</t>
+          <t>61629; 94761</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>194909; 244969</t>
+          <t>195297; 245183</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>172012; 221476</t>
+          <t>169986; 222767</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>56414; 91953</t>
+          <t>56317; 91384</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>108177; 139098</t>
+          <t>125732; 162095</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>380909; 451952</t>
+          <t>378157; 450304</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>290277; 362805</t>
+          <t>291432; 360264</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>92140; 134979</t>
+          <t>92736; 135194</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>119352; 233563</t>
+          <t>196715; 245516</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>434995</t>
+          <t>472094</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>858503</t>
+          <t>727593</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1293498</t>
+          <t>1199687</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>513326; 598104</t>
+          <t>512557; 598780</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>499111; 596268</t>
+          <t>495542; 587182</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>358217; 431445</t>
+          <t>360374; 434948</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>341352; 487179</t>
+          <t>430206; 515362</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>711226; 805335</t>
+          <t>710915; 807951</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>871659; 977191</t>
+          <t>867361; 978350</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>545872; 637115</t>
+          <t>542145; 637600</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>676326; 1420058</t>
+          <t>686740; 769919</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1249092; 1376110</t>
+          <t>1241836; 1377343</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1395615; 1537357</t>
+          <t>1390928; 1532087</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>929739; 1047161</t>
+          <t>926230; 1045018</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1084551; 1891444</t>
+          <t>1138565; 1259407</t>
         </is>
       </c>
     </row>
